--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_80_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_80_R8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0507</v>
+        <v>6.2923</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1536</v>
+        <v>2.98</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8971</v>
+        <v>3.3123</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5173</v>
+        <v>2.5656</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.093</v>
+        <v>0.702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5757</v>
+        <v>1.8636</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2693</v>
+        <v>2.5115</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6814</v>
+        <v>0.4306</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9507</v>
+        <v>2.0809</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7865</v>
+        <v>0.0541</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4116</v>
+        <v>0.2714</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.375</v>
+        <v>-0.2173</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7304</v>
+        <v>0.8659</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2244</v>
+        <v>0.2519</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5059</v>
+        <v>0.6139</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.3969</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8197</v>
+        <v>1.6083</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6177</v>
+        <v>3.4139</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6079</v>
+        <v>1.9872</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0098</v>
+        <v>1.4266</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5656</v>
+        <v>-0.5173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.702</v>
+        <v>-1.093</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8636</v>
+        <v>0.5757</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5115</v>
+        <v>1.2693</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4306</v>
+        <v>-0.6814</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0809</v>
+        <v>1.9507</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0541</v>
+        <v>-1.7865</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2714</v>
+        <v>-0.4116</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2173</v>
+        <v>-1.375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8087</v>
+        <v>2.0935</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1202</v>
+        <v>1.058</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3115</v>
+        <v>1.0354</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3969</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>0.8197</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7886</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3679</v>
+        <v>2.6011</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5036</v>
+        <v>-0.9008</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8716</v>
+        <v>3.5019</v>
       </c>
       <c r="G4" t="n">
         <v>1.3186</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5854</v>
+        <v>0.8186</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6018</v>
+        <v>0.2047</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9836</v>
+        <v>0.6139</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2369</v>
+        <v>1.1272</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3854</v>
+        <v>-0.3239</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1486</v>
+        <v>1.451</v>
       </c>
       <c r="G5" t="n">
         <v>0.0255</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6515</v>
+        <v>0.7125</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1202</v>
+        <v>-0.0587</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4687</v>
+        <v>0.7712</v>
       </c>
       <c r="V5" t="n">
         <v>-1.4665</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4896</v>
+        <v>-2.0299</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7078</v>
+        <v>1.7642</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1975</v>
+        <v>-3.7942</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0769</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4998</v>
+        <v>0.9594</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3882</v>
+        <v>0.4446</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1116</v>
+        <v>0.5149</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1444</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3204</v>
+        <v>-2.3431</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6805</v>
+        <v>-0.308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3602</v>
+        <v>-2.035</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1984</v>
+        <v>-3.5746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1668</v>
+        <v>-0.4093</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3652</v>
+        <v>-3.1652</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7661</v>
+        <v>0.1527</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0203</v>
+        <v>0.474</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7863</v>
+        <v>-0.3213</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4323</v>
+        <v>-3.7273</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1465</v>
+        <v>-0.8834</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5788</v>
+        <v>-2.8439</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9656</v>
+        <v>0.0512</v>
       </c>
       <c r="T7" t="n">
-        <v>0.637</v>
+        <v>-0.1412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3286</v>
+        <v>0.1924</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8045</v>
+        <v>-2.7414</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5007</v>
+        <v>-3.0344</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3039</v>
+        <v>0.2929</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5746</v>
+        <v>-1.1984</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4093</v>
+        <v>0.1668</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1652</v>
+        <v>-1.3652</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1527</v>
+        <v>-0.7661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.0203</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3213</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7273</v>
+        <v>-0.4323</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8834</v>
+        <v>0.1465</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.8439</v>
+        <v>-0.5788</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4103</v>
+        <v>0.5445</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3339</v>
+        <v>0.2831</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0764</v>
+        <v>0.2614</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9263</v>
+        <v>-3.7551</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.0876</v>
+        <v>-5.4795</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1613</v>
+        <v>1.7244</v>
       </c>
       <c r="G9" t="n">
         <v>-3.4585</v>
@@ -1156,13 +1156,13 @@
         <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1173</v>
+        <v>1.2885</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5683</v>
+        <v>0.0397</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6856</v>
+        <v>1.2487</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4254</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6644</v>
+        <v>-5.5972</v>
       </c>
       <c r="E10" t="n">
         <v>-3.8391</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8253</v>
+        <v>-1.7581</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1736</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4033</v>
+        <v>-0.3361</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4058</v>
+        <v>-3.0322</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.527600000000001</v>
+        <v>-7.1543</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1219</v>
+        <v>4.121800000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.089599999999999</v>
+        <v>-7.089600000000001</v>
       </c>
       <c r="H11" t="n">
         <v>1.3254</v>
@@ -1312,16 +1312,16 @@
         <v>15.0769</v>
       </c>
       <c r="S11" t="n">
-        <v>6.624700000000001</v>
+        <v>6.997999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2607</v>
+        <v>1.634</v>
       </c>
       <c r="U11" t="n">
-        <v>5.363900000000001</v>
+        <v>5.3638</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7812</v>
+        <v>-1.781200000000001</v>
       </c>
       <c r="W11" t="n">
         <v>3.3895</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.7229</v>
+        <v>12.8079</v>
       </c>
       <c r="E12" t="n">
-        <v>9.0753</v>
+        <v>9.4291</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6477</v>
+        <v>3.3788</v>
       </c>
       <c r="G12" t="n">
         <v>5.5192</v>
@@ -1390,13 +1390,13 @@
         <v>3.0154</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3839</v>
+        <v>-0.2989</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8883</v>
+        <v>-0.5344</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5043</v>
+        <v>0.2355</v>
       </c>
       <c r="V12" t="n">
         <v>4.5724</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.636</v>
+        <v>4.1407</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3711</v>
+        <v>1.607</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2649</v>
+        <v>2.5337</v>
       </c>
       <c r="G13" t="n">
         <v>4.3795</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3697</v>
+        <v>-0.865</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.507</v>
+        <v>-0.2711</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8628</v>
+        <v>-0.5939</v>
       </c>
       <c r="V13" t="n">
         <v>0.3943</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9111</v>
+        <v>2.8603</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4744</v>
+        <v>0.3565</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4366</v>
+        <v>2.5039</v>
       </c>
       <c r="G14" t="n">
         <v>4.2734</v>
@@ -1546,13 +1546,13 @@
         <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0403</v>
+        <v>-1.091</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.55</v>
+        <v>-0.668</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4902</v>
+        <v>-0.423</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2927</v>
+        <v>-0.1283</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9587</v>
+        <v>-1.3126</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2514</v>
+        <v>1.1842</v>
       </c>
       <c r="G15" t="n">
         <v>2.3612</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.4896</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0553</v>
+        <v>-0.2985</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1239</v>
+        <v>-0.1911</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5422</v>
+        <v>-0.3748</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8945</v>
+        <v>-1.1304</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3524</v>
+        <v>0.7556</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7759</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.094</v>
+        <v>-0.3299</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6001</v>
+        <v>-0.1968</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7919</v>
+        <v>-1.7247</v>
       </c>
       <c r="E17" t="n">
         <v>-1.1429</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.649</v>
+        <v>-0.5817</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6953</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3286</v>
+        <v>-0.2614</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2817</v>
+        <v>-2.2481</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0104</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2714</v>
+        <v>-1.2377</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0079</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2016</v>
+        <v>-0.168</v>
       </c>
       <c r="T18" t="n">
         <v>-0.224</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3397</v>
+        <v>-2.3562</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2447</v>
+        <v>-1.1267</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.095</v>
+        <v>-1.2295</v>
       </c>
       <c r="G19" t="n">
         <v>1.127</v>
@@ -1936,13 +1936,13 @@
         <v>2.5515</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2142</v>
+        <v>-1.2307</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8883</v>
+        <v>-0.7703</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3259</v>
+        <v>-0.4604</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3247</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.781</v>
+        <v>-2.9332</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.994</v>
+        <v>-2.9449</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2131</v>
+        <v>0.0117</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.0483</v>
+        <v>-0.0157</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5149</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.5334</v>
+        <v>-0.107</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1086</v>
+        <v>0.7564</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>0.0203</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.3222</v>
+        <v>0.7361</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9398</v>
+        <v>-0.7721</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2714</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2112</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.105</v>
+        <v>-0.5052</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0272</v>
+        <v>-0.735</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1322</v>
+        <v>0.2298</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9304</v>
+        <v>-0.7886</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>-0.6468</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7886</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9674</v>
+        <v>-3.0827</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1808</v>
+        <v>-3.3806</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2134</v>
+        <v>0.2979</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0157</v>
+        <v>-3.0278</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09130000000000001</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.107</v>
+        <v>-2.2319</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7564</v>
+        <v>-2.7204</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0203</v>
+        <v>-0.7527</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7361</v>
+        <v>-1.9676</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7721</v>
+        <v>-0.3074</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0431</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8431</v>
+        <v>-0.2643</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5395</v>
+        <v>-0.5188</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9709</v>
+        <v>-0.6603</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4314</v>
+        <v>0.1415</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.453</v>
+        <v>-3.5552</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6165</v>
+        <v>-3.4658</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1635</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0278</v>
+        <v>-4.0483</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.5149</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2319</v>
+        <v>-3.5334</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7204</v>
+        <v>-3.1086</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7527</v>
+        <v>-0.7863</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9676</v>
+        <v>-2.3222</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3074</v>
+        <v>-0.9398</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0431</v>
+        <v>0.2714</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2643</v>
+        <v>-1.2112</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8891</v>
+        <v>-0.6693</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.4991</v>
       </c>
       <c r="U22" t="n">
-        <v>0.007</v>
+        <v>-0.1702</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.405799999999999</v>
+        <v>3.405699999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.121699999999999</v>
+        <v>-4.121700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>7.5276</v>
+        <v>7.5275</v>
       </c>
       <c r="G23" t="n">
         <v>7.089399999999999</v>
@@ -2227,10 +2227,10 @@
         <v>2.1658</v>
       </c>
       <c r="L23" t="n">
-        <v>8.982800000000001</v>
+        <v>8.982800000000003</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.058800000000001</v>
+        <v>-4.0588</v>
       </c>
       <c r="N23" t="n">
         <v>-3.4909</v>
@@ -2239,7 +2239,7 @@
         <v>-0.5676999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>1.159900000000001</v>
+        <v>1.1599</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.0769</v>
@@ -2248,13 +2248,13 @@
         <v>16.2369</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.6245</v>
+        <v>-6.6246</v>
       </c>
       <c r="T23" t="n">
         <v>-5.364000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2608</v>
+        <v>-1.2606</v>
       </c>
       <c r="V23" t="n">
         <v>1.781200000000001</v>
